--- a/public/templates/trial-balance-template.xlsx
+++ b/public/templates/trial-balance-template.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/uzair/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5FC05B-F60A-5042-96A7-FB90C6005113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -148,22 +170,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -172,11 +197,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -190,75 +221,37 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -275,39 +268,63 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Sheet1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C42" displayName="Accounts" name="Accounts" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Accounts" displayName="Accounts" ref="A1:C42">
   <tableColumns count="3">
-    <tableColumn name="ID" id="1"/>
-    <tableColumn name="Account" id="2"/>
-    <tableColumn name="Amount" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Account"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Amount"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -497,22 +514,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.13"/>
-    <col customWidth="1" min="2" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="11.38"/>
+    <col min="1" max="1" width="4.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,18 +543,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A42" si="1">+A2+1</f>
+        <f t="shared" ref="A3:A42" si="0">+A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -542,9 +562,9 @@
       </c>
       <c r="C3" s="6"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -552,9 +572,9 @@
       </c>
       <c r="C4" s="6"/>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -562,9 +582,9 @@
       </c>
       <c r="C5" s="6"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -572,9 +592,9 @@
       </c>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -582,9 +602,9 @@
       </c>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -592,9 +612,9 @@
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -602,9 +622,9 @@
       </c>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -612,9 +632,9 @@
       </c>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -622,9 +642,9 @@
       </c>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -632,9 +652,9 @@
       </c>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -642,9 +662,9 @@
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -652,9 +672,9 @@
       </c>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -662,9 +682,9 @@
       </c>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -672,9 +692,9 @@
       </c>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -682,9 +702,9 @@
       </c>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -692,9 +712,9 @@
       </c>
       <c r="C18" s="6"/>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -702,9 +722,9 @@
       </c>
       <c r="C19" s="6"/>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -712,9 +732,9 @@
       </c>
       <c r="C20" s="6"/>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -722,9 +742,9 @@
       </c>
       <c r="C21" s="6"/>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
+    <row r="22" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -732,9 +752,9 @@
       </c>
       <c r="C22" s="6"/>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -742,9 +762,9 @@
       </c>
       <c r="C23" s="6"/>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -752,9 +772,9 @@
       </c>
       <c r="C24" s="6"/>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -762,9 +782,9 @@
       </c>
       <c r="C25" s="6"/>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
+    <row r="26" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
@@ -772,9 +792,9 @@
       </c>
       <c r="C26" s="6"/>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -782,9 +802,9 @@
       </c>
       <c r="C27" s="6"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -792,9 +812,9 @@
       </c>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
+    <row r="29" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -802,9 +822,9 @@
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
+    <row r="30" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -812,9 +832,9 @@
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
+    <row r="31" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -822,9 +842,9 @@
       </c>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
+    <row r="32" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -832,9 +852,9 @@
       </c>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
+    <row r="33" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -842,9 +862,9 @@
       </c>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
+    <row r="34" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -852,9 +872,9 @@
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
+    <row r="35" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -862,9 +882,9 @@
       </c>
       <c r="C35" s="6"/>
     </row>
-    <row r="36" ht="22.5" customHeight="1">
+    <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -872,9 +892,9 @@
       </c>
       <c r="C36" s="6"/>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
+    <row r="37" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -882,9 +902,9 @@
       </c>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" ht="22.5" customHeight="1">
+    <row r="38" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -892,9 +912,9 @@
       </c>
       <c r="C38" s="6"/>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
+    <row r="39" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -902,9 +922,9 @@
       </c>
       <c r="C39" s="6"/>
     </row>
-    <row r="40" ht="22.5" customHeight="1">
+    <row r="40" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -912,9 +932,9 @@
       </c>
       <c r="C40" s="6"/>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
+    <row r="41" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -922,9 +942,9 @@
       </c>
       <c r="C41" s="6"/>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
+    <row r="42" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
@@ -933,9 +953,9 @@
       <c r="C42" s="6"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>